--- a/Team-Data/2020-21/1-12-2020-21.xlsx
+++ b/Team-Data/2020-21/1-12-2020-21.xlsx
@@ -806,37 +806,37 @@
         <v>4.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AG2" t="n">
         <v>15</v>
       </c>
       <c r="AH2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ2" t="n">
         <v>11</v>
       </c>
       <c r="AK2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO2" t="n">
         <v>1</v>
@@ -851,7 +851,7 @@
         <v>1</v>
       </c>
       <c r="AS2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT2" t="n">
         <v>2</v>
@@ -863,13 +863,13 @@
         <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX2" t="n">
         <v>28</v>
       </c>
       <c r="AY2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ2" t="n">
         <v>21</v>
@@ -881,7 +881,7 @@
         <v>9</v>
       </c>
       <c r="BC2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -988,10 +988,10 @@
         <v>1.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AE3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
         <v>1</v>
@@ -1000,10 +1000,10 @@
         <v>2</v>
       </c>
       <c r="AH3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ3" t="n">
         <v>14</v>
@@ -1012,13 +1012,13 @@
         <v>6</v>
       </c>
       <c r="AL3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AN3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO3" t="n">
         <v>23</v>
@@ -1027,7 +1027,7 @@
         <v>20</v>
       </c>
       <c r="AQ3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR3" t="n">
         <v>4</v>
@@ -1036,22 +1036,22 @@
         <v>24</v>
       </c>
       <c r="AT3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
         <v>23</v>
       </c>
       <c r="AV3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW3" t="n">
         <v>6</v>
       </c>
       <c r="AX3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AZ3" t="n">
         <v>23</v>
@@ -1063,7 +1063,7 @@
         <v>12</v>
       </c>
       <c r="BC3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -1092,142 +1092,142 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5</v>
+        <v>0.455</v>
       </c>
       <c r="H4" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>42.8</v>
+        <v>42.3</v>
       </c>
       <c r="J4" t="n">
-        <v>87.7</v>
+        <v>88.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.488</v>
+        <v>0.478</v>
       </c>
       <c r="L4" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="M4" t="n">
-        <v>36.1</v>
+        <v>36.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.393</v>
+        <v>0.384</v>
       </c>
       <c r="O4" t="n">
-        <v>19.2</v>
+        <v>20</v>
       </c>
       <c r="P4" t="n">
-        <v>23.9</v>
+        <v>24.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.801</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="R4" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>37.8</v>
+        <v>38.2</v>
       </c>
       <c r="T4" t="n">
-        <v>46.4</v>
+        <v>46.9</v>
       </c>
       <c r="U4" t="n">
-        <v>25.9</v>
+        <v>25.5</v>
       </c>
       <c r="V4" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="W4" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X4" t="n">
         <v>5.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>118.8</v>
+        <v>118.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AD4" t="n">
         <v>1</v>
       </c>
       <c r="AE4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AF4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG4" t="n">
         <v>19</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AH4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>15</v>
       </c>
-      <c r="AH4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>18</v>
-      </c>
       <c r="AK4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AL4" t="n">
         <v>6</v>
       </c>
       <c r="AM4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AO4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AP4" t="n">
         <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR4" t="n">
         <v>21</v>
       </c>
       <c r="AS4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AT4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AV4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AX4" t="n">
         <v>7</v>
@@ -1236,10 +1236,10 @@
         <v>6</v>
       </c>
       <c r="AZ4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA4" t="n">
         <v>9</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>10</v>
       </c>
       <c r="BB4" t="n">
         <v>3</v>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -1352,19 +1352,19 @@
         <v>0.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AF5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AG5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI5" t="n">
         <v>25</v>
@@ -1379,16 +1379,16 @@
         <v>14</v>
       </c>
       <c r="AM5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN5" t="n">
         <v>12</v>
       </c>
       <c r="AO5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ5" t="n">
         <v>21</v>
@@ -1406,19 +1406,19 @@
         <v>1</v>
       </c>
       <c r="AV5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW5" t="n">
         <v>4</v>
       </c>
       <c r="AX5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY5" t="n">
         <v>12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA5" t="n">
         <v>16</v>
@@ -1427,7 +1427,7 @@
         <v>24</v>
       </c>
       <c r="BC5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -1534,19 +1534,19 @@
         <v>-5</v>
       </c>
       <c r="AD6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>22</v>
       </c>
       <c r="AF6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI6" t="n">
         <v>9</v>
@@ -1558,25 +1558,25 @@
         <v>9</v>
       </c>
       <c r="AL6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AN6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AO6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ6" t="n">
         <v>3</v>
       </c>
       <c r="AR6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS6" t="n">
         <v>16</v>
@@ -1591,10 +1591,10 @@
         <v>30</v>
       </c>
       <c r="AW6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY6" t="n">
         <v>9</v>
@@ -1603,13 +1603,13 @@
         <v>24</v>
       </c>
       <c r="BA6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB6" t="n">
         <v>6</v>
       </c>
       <c r="BC6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -1638,115 +1638,115 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>0.417</v>
+        <v>0.455</v>
       </c>
       <c r="H7" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="I7" t="n">
-        <v>38.5</v>
+        <v>38.8</v>
       </c>
       <c r="J7" t="n">
-        <v>87.2</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.442</v>
+        <v>0.447</v>
       </c>
       <c r="L7" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>27.8</v>
+        <v>27.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.344</v>
+        <v>0.353</v>
       </c>
       <c r="O7" t="n">
-        <v>12.3</v>
+        <v>12.6</v>
       </c>
       <c r="P7" t="n">
-        <v>18.9</v>
+        <v>19.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.652</v>
+        <v>0.653</v>
       </c>
       <c r="R7" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S7" t="n">
-        <v>32.4</v>
+        <v>32.8</v>
       </c>
       <c r="T7" t="n">
-        <v>43.5</v>
+        <v>43.8</v>
       </c>
       <c r="U7" t="n">
         <v>23.7</v>
       </c>
       <c r="V7" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="W7" t="n">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
       <c r="X7" t="n">
         <v>4.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.9</v>
+        <v>19.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>98.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="AC7" t="n">
-        <v>-5.1</v>
+        <v>-2.8</v>
       </c>
       <c r="AD7" t="n">
         <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AF7" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AG7" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AH7" t="n">
         <v>3</v>
       </c>
       <c r="AI7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ7" t="n">
         <v>21</v>
       </c>
       <c r="AK7" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AL7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM7" t="n">
         <v>29</v>
       </c>
       <c r="AN7" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
         <v>30</v>
@@ -1761,25 +1761,25 @@
         <v>8</v>
       </c>
       <c r="AS7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AU7" t="n">
         <v>18</v>
       </c>
       <c r="AV7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW7" t="n">
         <v>1</v>
       </c>
       <c r="AX7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AY7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
         <v>8</v>
@@ -1791,7 +1791,7 @@
         <v>30</v>
       </c>
       <c r="BC7" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -1898,28 +1898,28 @@
         <v>4.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AF8" t="n">
         <v>3</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AJ8" t="n">
         <v>29</v>
       </c>
       <c r="AK8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL8" t="n">
         <v>9</v>
@@ -1928,10 +1928,10 @@
         <v>7</v>
       </c>
       <c r="AN8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP8" t="n">
         <v>5</v>
@@ -1940,7 +1940,7 @@
         <v>14</v>
       </c>
       <c r="AR8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS8" t="n">
         <v>15</v>
@@ -1955,7 +1955,7 @@
         <v>8</v>
       </c>
       <c r="AW8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX8" t="n">
         <v>24</v>
@@ -1970,10 +1970,10 @@
         <v>1</v>
       </c>
       <c r="BB8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BC8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -2002,22 +2002,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.455</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="I9" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="J9" t="n">
         <v>87.5</v>
@@ -2026,100 +2026,100 @@
         <v>0.494</v>
       </c>
       <c r="L9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="M9" t="n">
-        <v>33.8</v>
+        <v>33.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0.384</v>
+        <v>0.373</v>
       </c>
       <c r="O9" t="n">
-        <v>16.9</v>
+        <v>17.6</v>
       </c>
       <c r="P9" t="n">
-        <v>23</v>
+        <v>23.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.735</v>
+        <v>0.743</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="S9" t="n">
-        <v>31.7</v>
+        <v>32.6</v>
       </c>
       <c r="T9" t="n">
-        <v>41.7</v>
+        <v>42.7</v>
       </c>
       <c r="U9" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="V9" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="W9" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="X9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.5</v>
+        <v>20.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="AB9" t="n">
         <v>116.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AE9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG9" t="n">
         <v>15</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>18</v>
       </c>
       <c r="AH9" t="n">
         <v>2</v>
       </c>
       <c r="AI9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AM9" t="n">
         <v>19</v>
       </c>
       <c r="AN9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AO9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AP9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AQ9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR9" t="n">
         <v>14</v>
@@ -2128,16 +2128,16 @@
         <v>29</v>
       </c>
       <c r="AT9" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AU9" t="n">
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX9" t="n">
         <v>22</v>
@@ -2146,16 +2146,16 @@
         <v>7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB9" t="n">
         <v>5</v>
       </c>
       <c r="BC9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -2229,16 +2229,16 @@
         <v>11.1</v>
       </c>
       <c r="S10" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T10" t="n">
-        <v>43.7</v>
+        <v>43.8</v>
       </c>
       <c r="U10" t="n">
         <v>23.6</v>
       </c>
       <c r="V10" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W10" t="n">
         <v>8.4</v>
@@ -2262,7 +2262,7 @@
         <v>-6.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
         <v>29</v>
@@ -2277,7 +2277,7 @@
         <v>1</v>
       </c>
       <c r="AI10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ10" t="n">
         <v>2</v>
@@ -2286,37 +2286,37 @@
         <v>30</v>
       </c>
       <c r="AL10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AM10" t="n">
         <v>10</v>
       </c>
       <c r="AN10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP10" t="n">
         <v>13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AR10" t="n">
         <v>7</v>
       </c>
       <c r="AS10" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU10" t="n">
         <v>19</v>
       </c>
       <c r="AV10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW10" t="n">
         <v>9</v>
@@ -2325,16 +2325,16 @@
         <v>21</v>
       </c>
       <c r="AY10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ10" t="n">
         <v>12</v>
       </c>
       <c r="BA10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC10" t="n">
         <v>28</v>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -2366,136 +2366,136 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>0.545</v>
+        <v>0.6</v>
       </c>
       <c r="H11" t="n">
         <v>48</v>
       </c>
       <c r="I11" t="n">
-        <v>39.4</v>
+        <v>39.9</v>
       </c>
       <c r="J11" t="n">
-        <v>90.2</v>
+        <v>90.3</v>
       </c>
       <c r="K11" t="n">
-        <v>0.436</v>
+        <v>0.442</v>
       </c>
       <c r="L11" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="M11" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="N11" t="n">
         <v>0.351</v>
       </c>
       <c r="O11" t="n">
-        <v>19.7</v>
+        <v>20.3</v>
       </c>
       <c r="P11" t="n">
-        <v>24.8</v>
+        <v>25.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.795</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S11" t="n">
         <v>35.7</v>
       </c>
       <c r="T11" t="n">
-        <v>44.2</v>
+        <v>44</v>
       </c>
       <c r="U11" t="n">
         <v>24.9</v>
       </c>
       <c r="V11" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W11" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X11" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>21.9</v>
+        <v>22.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>112</v>
+        <v>113.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>-3.5</v>
+        <v>-2.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AE11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AF11" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AH11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AJ11" t="n">
         <v>9</v>
       </c>
       <c r="AK11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL11" t="n">
         <v>10</v>
       </c>
       <c r="AM11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP11" t="n">
         <v>6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AR11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV11" t="n">
         <v>13</v>
@@ -2507,19 +2507,19 @@
         <v>5</v>
       </c>
       <c r="AY11" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BB11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BC11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -2548,55 +2548,55 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="H12" t="n">
         <v>48.6</v>
       </c>
       <c r="I12" t="n">
-        <v>40</v>
+        <v>40.3</v>
       </c>
       <c r="J12" t="n">
-        <v>86.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.464</v>
+        <v>0.474</v>
       </c>
       <c r="L12" t="n">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
       <c r="M12" t="n">
-        <v>38.8</v>
+        <v>38.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0.338</v>
+        <v>0.343</v>
       </c>
       <c r="O12" t="n">
-        <v>18.2</v>
+        <v>19</v>
       </c>
       <c r="P12" t="n">
-        <v>23.9</v>
+        <v>24.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R12" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="S12" t="n">
-        <v>34.2</v>
+        <v>34.5</v>
       </c>
       <c r="T12" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U12" t="n">
         <v>23.1</v>
@@ -2605,103 +2605,103 @@
         <v>15.1</v>
       </c>
       <c r="W12" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="X12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.1</v>
+        <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="AB12" t="n">
-        <v>111.3</v>
+        <v>112.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.9</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AE12" t="n">
         <v>26</v>
       </c>
       <c r="AF12" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AG12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH12" t="n">
         <v>4</v>
       </c>
       <c r="AI12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AJ12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AK12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AL12" t="n">
         <v>13</v>
       </c>
       <c r="AM12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN12" t="n">
         <v>24</v>
       </c>
       <c r="AO12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AP12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU12" t="n">
         <v>24</v>
       </c>
       <c r="AV12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AX12" t="n">
         <v>2</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -2730,115 +2730,115 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>0.636</v>
+        <v>0.6</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
       </c>
       <c r="I13" t="n">
-        <v>43.5</v>
+        <v>44</v>
       </c>
       <c r="J13" t="n">
-        <v>89.90000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.484</v>
+        <v>0.488</v>
       </c>
       <c r="L13" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="M13" t="n">
-        <v>33.5</v>
+        <v>34</v>
       </c>
       <c r="N13" t="n">
-        <v>0.361</v>
+        <v>0.365</v>
       </c>
       <c r="O13" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="P13" t="n">
-        <v>20.6</v>
+        <v>20.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.749</v>
+        <v>0.757</v>
       </c>
       <c r="R13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="S13" t="n">
-        <v>34.3</v>
+        <v>33.7</v>
       </c>
       <c r="T13" t="n">
-        <v>42.5</v>
+        <v>41.7</v>
       </c>
       <c r="U13" t="n">
         <v>26.4</v>
       </c>
       <c r="V13" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W13" t="n">
         <v>9.5</v>
       </c>
       <c r="X13" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>22.1</v>
+        <v>22.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="AB13" t="n">
-        <v>114.6</v>
+        <v>115.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AF13" t="n">
         <v>3</v>
       </c>
       <c r="AG13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK13" t="n">
         <v>4</v>
       </c>
-      <c r="AH13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>5</v>
-      </c>
       <c r="AL13" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AM13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AN13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO13" t="n">
         <v>25</v>
@@ -2847,43 +2847,43 @@
         <v>23</v>
       </c>
       <c r="AQ13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR13" t="n">
         <v>25</v>
       </c>
       <c r="AS13" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AT13" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AU13" t="n">
         <v>5</v>
       </c>
       <c r="AV13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW13" t="n">
         <v>3</v>
       </c>
       <c r="AX13" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AY13" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AZ13" t="n">
         <v>27</v>
       </c>
       <c r="BA13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -2990,25 +2990,25 @@
         <v>1</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>3</v>
       </c>
       <c r="AG14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK14" t="n">
         <v>11</v>
@@ -3026,13 +3026,13 @@
         <v>17</v>
       </c>
       <c r="AP14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ14" t="n">
         <v>1</v>
       </c>
       <c r="AR14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS14" t="n">
         <v>30</v>
@@ -3047,7 +3047,7 @@
         <v>12</v>
       </c>
       <c r="AW14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX14" t="n">
         <v>15</v>
@@ -3065,7 +3065,7 @@
         <v>14</v>
       </c>
       <c r="BC14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -3094,82 +3094,82 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>0.75</v>
+        <v>0.727</v>
       </c>
       <c r="H15" t="n">
         <v>48</v>
       </c>
       <c r="I15" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="J15" t="n">
-        <v>87.5</v>
+        <v>87.8</v>
       </c>
       <c r="K15" t="n">
         <v>0.493</v>
       </c>
       <c r="L15" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="M15" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0.389</v>
+        <v>0.385</v>
       </c>
       <c r="O15" t="n">
-        <v>16.2</v>
+        <v>15.9</v>
       </c>
       <c r="P15" t="n">
-        <v>21.3</v>
+        <v>20.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.758</v>
+        <v>0.764</v>
       </c>
       <c r="R15" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="S15" t="n">
-        <v>38.8</v>
+        <v>38.3</v>
       </c>
       <c r="T15" t="n">
-        <v>48.8</v>
+        <v>48.2</v>
       </c>
       <c r="U15" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="V15" t="n">
-        <v>15.9</v>
+        <v>15.5</v>
       </c>
       <c r="W15" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="X15" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z15" t="n">
         <v>18.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>114.7</v>
+        <v>114.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AD15" t="n">
         <v>1</v>
@@ -3184,55 +3184,55 @@
         <v>1</v>
       </c>
       <c r="AH15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AK15" t="n">
         <v>3</v>
       </c>
       <c r="AL15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AM15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AN15" t="n">
         <v>6</v>
       </c>
       <c r="AO15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP15" t="n">
         <v>19</v>
       </c>
-      <c r="AP15" t="n">
-        <v>18</v>
-      </c>
       <c r="AQ15" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AR15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU15" t="n">
         <v>12</v>
       </c>
       <c r="AV15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AW15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AX15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY15" t="n">
         <v>10</v>
@@ -3244,7 +3244,7 @@
         <v>15</v>
       </c>
       <c r="BB15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC15" t="n">
         <v>2</v>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -3354,19 +3354,19 @@
         <v>-2.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AE16" t="n">
         <v>22</v>
       </c>
       <c r="AF16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AG16" t="n">
         <v>24</v>
       </c>
       <c r="AH16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI16" t="n">
         <v>13</v>
@@ -3384,7 +3384,7 @@
         <v>23</v>
       </c>
       <c r="AN16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO16" t="n">
         <v>28</v>
@@ -3393,13 +3393,13 @@
         <v>30</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR16" t="n">
         <v>12</v>
       </c>
       <c r="AS16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT16" t="n">
         <v>10</v>
@@ -3408,19 +3408,19 @@
         <v>6</v>
       </c>
       <c r="AV16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW16" t="n">
         <v>2</v>
       </c>
       <c r="AX16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA16" t="n">
         <v>30</v>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -3458,130 +3458,130 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
         <v>4</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>0.444</v>
+        <v>0.5</v>
       </c>
       <c r="H17" t="n">
-        <v>48.6</v>
+        <v>48</v>
       </c>
       <c r="I17" t="n">
-        <v>40.1</v>
+        <v>39.1</v>
       </c>
       <c r="J17" t="n">
-        <v>84</v>
+        <v>81.5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.478</v>
+        <v>0.48</v>
       </c>
       <c r="L17" t="n">
-        <v>13.3</v>
+        <v>12.6</v>
       </c>
       <c r="M17" t="n">
-        <v>37.2</v>
+        <v>34.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0.358</v>
+        <v>0.362</v>
       </c>
       <c r="O17" t="n">
-        <v>17.8</v>
+        <v>17.6</v>
       </c>
       <c r="P17" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.769</v>
+        <v>0.766</v>
       </c>
       <c r="R17" t="n">
-        <v>7</v>
+        <v>6.1</v>
       </c>
       <c r="S17" t="n">
-        <v>37.1</v>
+        <v>37.8</v>
       </c>
       <c r="T17" t="n">
-        <v>44.1</v>
+        <v>43.9</v>
       </c>
       <c r="U17" t="n">
         <v>26.8</v>
       </c>
       <c r="V17" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="W17" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="X17" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA17" t="n">
         <v>21.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>111.3</v>
+        <v>108.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>-1.3</v>
+        <v>-1.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AE17" t="n">
         <v>22</v>
       </c>
       <c r="AF17" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AG17" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AH17" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="AI17" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AL17" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AM17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AN17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO17" t="n">
         <v>12</v>
       </c>
       <c r="AP17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ17" t="n">
         <v>13</v>
       </c>
       <c r="AR17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT17" t="n">
         <v>18</v>
@@ -3593,22 +3593,22 @@
         <v>29</v>
       </c>
       <c r="AW17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA17" t="n">
         <v>8</v>
       </c>
       <c r="BB17" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="BC17" t="n">
         <v>18</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -3718,19 +3718,19 @@
         <v>11.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
         <v>3</v>
       </c>
       <c r="AG18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI18" t="n">
         <v>1</v>
@@ -3739,13 +3739,13 @@
         <v>7</v>
       </c>
       <c r="AK18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL18" t="n">
         <v>1</v>
       </c>
       <c r="AM18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN18" t="n">
         <v>2</v>
@@ -3754,7 +3754,7 @@
         <v>22</v>
       </c>
       <c r="AP18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ18" t="n">
         <v>18</v>
@@ -3766,7 +3766,7 @@
         <v>9</v>
       </c>
       <c r="AT18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
@@ -3784,10 +3784,10 @@
         <v>15</v>
       </c>
       <c r="AZ18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB18" t="n">
         <v>1</v>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -3900,19 +3900,19 @@
         <v>-10</v>
       </c>
       <c r="AD19" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AE19" t="n">
         <v>26</v>
       </c>
       <c r="AF19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG19" t="n">
         <v>27</v>
       </c>
       <c r="AH19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI19" t="n">
         <v>13</v>
@@ -3921,7 +3921,7 @@
         <v>5</v>
       </c>
       <c r="AK19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
         <v>24</v>
@@ -3948,16 +3948,16 @@
         <v>26</v>
       </c>
       <c r="AT19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU19" t="n">
         <v>21</v>
       </c>
       <c r="AV19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX19" t="n">
         <v>16</v>
@@ -3972,7 +3972,7 @@
         <v>21</v>
       </c>
       <c r="BB19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC19" t="n">
         <v>30</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -4082,28 +4082,28 @@
         <v>0.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE20" t="n">
         <v>22</v>
       </c>
       <c r="AF20" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AG20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AH20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
       </c>
       <c r="AJ20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL20" t="n">
         <v>27</v>
@@ -4115,7 +4115,7 @@
         <v>30</v>
       </c>
       <c r="AO20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP20" t="n">
         <v>3</v>
@@ -4127,16 +4127,16 @@
         <v>6</v>
       </c>
       <c r="AS20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU20" t="n">
         <v>22</v>
       </c>
       <c r="AV20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW20" t="n">
         <v>7</v>
@@ -4145,13 +4145,13 @@
         <v>25</v>
       </c>
       <c r="AY20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ20" t="n">
         <v>2</v>
       </c>
       <c r="BA20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB20" t="n">
         <v>25</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -4264,19 +4264,19 @@
         <v>-5.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH21" t="n">
         <v>15</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>17</v>
       </c>
       <c r="AI21" t="n">
         <v>30</v>
@@ -4285,7 +4285,7 @@
         <v>28</v>
       </c>
       <c r="AK21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL21" t="n">
         <v>30</v>
@@ -4294,13 +4294,13 @@
         <v>30</v>
       </c>
       <c r="AN21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO21" t="n">
         <v>24</v>
       </c>
       <c r="AP21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ21" t="n">
         <v>25</v>
@@ -4318,10 +4318,10 @@
         <v>28</v>
       </c>
       <c r="AV21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX21" t="n">
         <v>17</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -4368,154 +4368,154 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
         <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5</v>
+        <v>0.556</v>
       </c>
       <c r="H22" t="n">
         <v>48</v>
       </c>
       <c r="I22" t="n">
-        <v>38.3</v>
+        <v>38.6</v>
       </c>
       <c r="J22" t="n">
-        <v>85.3</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.449</v>
+        <v>0.451</v>
       </c>
       <c r="L22" t="n">
-        <v>12.9</v>
+        <v>13.6</v>
       </c>
       <c r="M22" t="n">
-        <v>39</v>
+        <v>40.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0.331</v>
+        <v>0.335</v>
       </c>
       <c r="O22" t="n">
-        <v>15.1</v>
+        <v>14.2</v>
       </c>
       <c r="P22" t="n">
-        <v>20.8</v>
+        <v>19.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.726</v>
+        <v>0.715</v>
       </c>
       <c r="R22" t="n">
         <v>7</v>
       </c>
       <c r="S22" t="n">
-        <v>38.4</v>
+        <v>37.7</v>
       </c>
       <c r="T22" t="n">
-        <v>45.4</v>
+        <v>44.7</v>
       </c>
       <c r="U22" t="n">
-        <v>21.8</v>
+        <v>22.2</v>
       </c>
       <c r="V22" t="n">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="W22" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="X22" t="n">
         <v>5.2</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB22" t="n">
-        <v>104.6</v>
+        <v>104.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>-4.6</v>
+        <v>-4</v>
       </c>
       <c r="AD22" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AE22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH22" t="n">
         <v>15</v>
       </c>
-      <c r="AF22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>17</v>
-      </c>
       <c r="AI22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ22" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AK22" t="n">
         <v>18</v>
       </c>
       <c r="AL22" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AM22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AN22" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO22" t="n">
         <v>27</v>
       </c>
       <c r="AP22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AQ22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR22" t="n">
         <v>29</v>
       </c>
       <c r="AS22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AT22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU22" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AV22" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AW22" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AX22" t="n">
         <v>12</v>
       </c>
       <c r="AY22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AZ22" t="n">
         <v>6</v>
       </c>
       <c r="BA22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB22" t="n">
         <v>28</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -4628,19 +4628,19 @@
         <v>-4.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AF23" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AG23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI23" t="n">
         <v>20</v>
@@ -4652,7 +4652,7 @@
         <v>29</v>
       </c>
       <c r="AL23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM23" t="n">
         <v>28</v>
@@ -4664,7 +4664,7 @@
         <v>17</v>
       </c>
       <c r="AP23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ23" t="n">
         <v>4</v>
@@ -4676,22 +4676,22 @@
         <v>16</v>
       </c>
       <c r="AT23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU23" t="n">
         <v>30</v>
       </c>
       <c r="AV23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX23" t="n">
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ23" t="n">
         <v>1</v>
@@ -4703,7 +4703,7 @@
         <v>26</v>
       </c>
       <c r="BC23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -4732,79 +4732,79 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F24" t="n">
         <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>0.667</v>
+        <v>0.636</v>
       </c>
       <c r="H24" t="n">
-        <v>48.4</v>
+        <v>48</v>
       </c>
       <c r="I24" t="n">
-        <v>42.1</v>
+        <v>41.4</v>
       </c>
       <c r="J24" t="n">
-        <v>89</v>
+        <v>87.8</v>
       </c>
       <c r="K24" t="n">
-        <v>0.473</v>
+        <v>0.471</v>
       </c>
       <c r="L24" t="n">
-        <v>12.2</v>
+        <v>11.5</v>
       </c>
       <c r="M24" t="n">
-        <v>34</v>
+        <v>32.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.358</v>
+        <v>0.36</v>
       </c>
       <c r="O24" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P24" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.759</v>
+        <v>0.763</v>
       </c>
       <c r="R24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>38</v>
+        <v>38.2</v>
       </c>
       <c r="T24" t="n">
-        <v>47.8</v>
+        <v>47.4</v>
       </c>
       <c r="U24" t="n">
-        <v>25.8</v>
+        <v>25.3</v>
       </c>
       <c r="V24" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="W24" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="X24" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z24" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA24" t="n">
         <v>20.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>113.4</v>
+        <v>111.3</v>
       </c>
       <c r="AC24" t="n">
         <v>2.5</v>
@@ -4825,55 +4825,55 @@
         <v>15</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AJ24" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AK24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL24" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AM24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AN24" t="n">
         <v>18</v>
       </c>
-      <c r="AN24" t="n">
-        <v>19</v>
-      </c>
       <c r="AO24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP24" t="n">
         <v>15</v>
       </c>
       <c r="AQ24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR24" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AS24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT24" t="n">
         <v>5</v>
       </c>
       <c r="AU24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV24" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AW24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX24" t="n">
         <v>1</v>
       </c>
       <c r="AY24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ24" t="n">
         <v>13</v>
@@ -4882,10 +4882,10 @@
         <v>14</v>
       </c>
       <c r="BB24" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BC24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -4992,28 +4992,28 @@
         <v>3.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF25" t="n">
         <v>3</v>
       </c>
       <c r="AG25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AH25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI25" t="n">
         <v>16</v>
       </c>
       <c r="AJ25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL25" t="n">
         <v>8</v>
@@ -5025,10 +5025,10 @@
         <v>13</v>
       </c>
       <c r="AO25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ25" t="n">
         <v>2</v>
@@ -5040,10 +5040,10 @@
         <v>18</v>
       </c>
       <c r="AT25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV25" t="n">
         <v>3</v>
@@ -5055,7 +5055,7 @@
         <v>20</v>
       </c>
       <c r="AY25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AZ25" t="n">
         <v>22</v>
@@ -5064,7 +5064,7 @@
         <v>16</v>
       </c>
       <c r="BB25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC25" t="n">
         <v>7</v>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -5174,19 +5174,19 @@
         <v>1.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AF26" t="n">
         <v>3</v>
       </c>
       <c r="AG26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AH26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI26" t="n">
         <v>12</v>
@@ -5195,7 +5195,7 @@
         <v>4</v>
       </c>
       <c r="AK26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL26" t="n">
         <v>2</v>
@@ -5204,22 +5204,22 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR26" t="n">
         <v>24</v>
       </c>
       <c r="AS26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT26" t="n">
         <v>15</v>
@@ -5234,22 +5234,22 @@
         <v>8</v>
       </c>
       <c r="AX26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB26" t="n">
         <v>4</v>
       </c>
       <c r="BC26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -5356,19 +5356,19 @@
         <v>-7.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AF27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG27" t="n">
         <v>19</v>
       </c>
-      <c r="AG27" t="n">
-        <v>18</v>
-      </c>
       <c r="AH27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI27" t="n">
         <v>11</v>
@@ -5377,7 +5377,7 @@
         <v>16</v>
       </c>
       <c r="AK27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL27" t="n">
         <v>25</v>
@@ -5386,22 +5386,22 @@
         <v>27</v>
       </c>
       <c r="AN27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP27" t="n">
         <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR27" t="n">
         <v>11</v>
       </c>
       <c r="AS27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT27" t="n">
         <v>16</v>
@@ -5416,13 +5416,13 @@
         <v>26</v>
       </c>
       <c r="AX27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AY27" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AZ27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA27" t="n">
         <v>7</v>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -5460,100 +5460,100 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F28" t="n">
         <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>0.545</v>
+        <v>0.5</v>
       </c>
       <c r="H28" t="n">
         <v>48.5</v>
       </c>
       <c r="I28" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="J28" t="n">
-        <v>94.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L28" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="M28" t="n">
-        <v>31.3</v>
+        <v>30.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.381</v>
+        <v>0.392</v>
       </c>
       <c r="O28" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="P28" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.787</v>
+        <v>0.773</v>
       </c>
       <c r="R28" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>36.4</v>
+        <v>36.1</v>
       </c>
       <c r="T28" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
       <c r="U28" t="n">
         <v>25.5</v>
       </c>
       <c r="V28" t="n">
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
       <c r="W28" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="X28" t="n">
         <v>5.1</v>
       </c>
       <c r="Y28" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>111.2</v>
+        <v>111.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>-0.9</v>
+        <v>-2</v>
       </c>
       <c r="AD28" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AE28" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AF28" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AG28" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AH28" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AI28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ28" t="n">
         <v>1</v>
@@ -5562,34 +5562,34 @@
         <v>23</v>
       </c>
       <c r="AL28" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AM28" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AN28" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AO28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT28" t="n">
         <v>11</v>
       </c>
       <c r="AU28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AV28" t="n">
         <v>1</v>
@@ -5601,19 +5601,19 @@
         <v>14</v>
       </c>
       <c r="AY28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA28" t="n">
         <v>22</v>
       </c>
       <c r="BB28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC28" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -5720,7 +5720,7 @@
         <v>-1.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AE29" t="n">
         <v>29</v>
@@ -5732,25 +5732,25 @@
         <v>29</v>
       </c>
       <c r="AH29" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ29" t="n">
         <v>12</v>
       </c>
       <c r="AK29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM29" t="n">
         <v>1</v>
       </c>
       <c r="AN29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO29" t="n">
         <v>16</v>
@@ -5759,16 +5759,16 @@
         <v>16</v>
       </c>
       <c r="AQ29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU29" t="n">
         <v>19</v>
@@ -5786,13 +5786,13 @@
         <v>30</v>
       </c>
       <c r="AZ29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA29" t="n">
         <v>23</v>
       </c>
       <c r="BB29" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BC29" t="n">
         <v>19</v>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -5824,160 +5824,160 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F30" t="n">
         <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>0.636</v>
+        <v>0.6</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="J30" t="n">
-        <v>88.7</v>
+        <v>89.2</v>
       </c>
       <c r="K30" t="n">
-        <v>0.457</v>
+        <v>0.453</v>
       </c>
       <c r="L30" t="n">
-        <v>15.9</v>
+        <v>15.1</v>
       </c>
       <c r="M30" t="n">
-        <v>40.7</v>
+        <v>40.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0.391</v>
+        <v>0.375</v>
       </c>
       <c r="O30" t="n">
-        <v>13.2</v>
+        <v>13.6</v>
       </c>
       <c r="P30" t="n">
-        <v>18.8</v>
+        <v>19.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.7</v>
+        <v>0.697</v>
       </c>
       <c r="R30" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S30" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="T30" t="n">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
       <c r="U30" t="n">
-        <v>22.5</v>
+        <v>22.1</v>
       </c>
       <c r="V30" t="n">
-        <v>15.4</v>
+        <v>15.1</v>
       </c>
       <c r="W30" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="X30" t="n">
         <v>5.5</v>
       </c>
-      <c r="X30" t="n">
-        <v>5.7</v>
-      </c>
       <c r="Y30" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="AA30" t="n">
-        <v>18.6</v>
+        <v>19.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>110.2</v>
+        <v>109.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AE30" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AF30" t="n">
         <v>3</v>
       </c>
       <c r="AG30" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AH30" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI30" t="n">
         <v>15</v>
       </c>
       <c r="AJ30" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AK30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AL30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AO30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP30" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AQ30" t="n">
         <v>29</v>
       </c>
       <c r="AR30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT30" t="n">
         <v>1</v>
       </c>
       <c r="AU30" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AV30" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AW30" t="n">
         <v>30</v>
       </c>
       <c r="AX30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AZ30" t="n">
         <v>3</v>
       </c>
       <c r="BA30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB30" t="n">
         <v>20</v>
       </c>
       <c r="BC30" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
         <v>-0.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE31" t="n">
         <v>26</v>
@@ -6096,16 +6096,16 @@
         <v>28</v>
       </c>
       <c r="AH31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ31" t="n">
         <v>3</v>
       </c>
       <c r="AK31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL31" t="n">
         <v>15</v>
@@ -6114,22 +6114,22 @@
         <v>20</v>
       </c>
       <c r="AN31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP31" t="n">
         <v>2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT31" t="n">
         <v>25</v>
@@ -6138,7 +6138,7 @@
         <v>2</v>
       </c>
       <c r="AV31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW31" t="n">
         <v>20</v>
@@ -6147,19 +6147,19 @@
         <v>29</v>
       </c>
       <c r="AY31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ31" t="n">
         <v>30</v>
       </c>
       <c r="BA31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BB31" t="n">
         <v>2</v>
       </c>
       <c r="BC31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-12-2020-21</t>
+          <t>2021-01-12</t>
         </is>
       </c>
     </row>
